--- a/SGC-CKN/Excel/d7dcd791-064d-4e77-b744-f9e040cad08d_Lô_CT-02_179_D800_24-03-2026.xlsx
+++ b/SGC-CKN/Excel/d7dcd791-064d-4e77-b744-f9e040cad08d_Lô_CT-02_179_D800_24-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>179</t>
+    <t>P1-129</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/d7dcd791-064d-4e77-b744-f9e040cad08d_Lô_CT-02_179_D800_24-03-2026.xlsx
+++ b/SGC-CKN/Excel/d7dcd791-064d-4e77-b744-f9e040cad08d_Lô_CT-02_179_D800_24-03-2026.xlsx
@@ -125,7 +125,7 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">09:30
+    <t xml:space="preserve">08:30
 24/03/2026</t>
   </si>
   <si>
@@ -135,31 +135,27 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">09:40
+    <t xml:space="preserve">09:10
 24/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">11:10
+    <t>11</t>
+  </si>
+  <si>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:45
 24/03/2026</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:45
-24/03/2026</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">12:30
+    <t xml:space="preserve">10:30
 24/03/2026</t>
   </si>
   <si>
@@ -177,6 +173,10 @@
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:58
+24/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:31
@@ -1225,13 +1225,13 @@
         <v>-7</v>
       </c>
       <c r="H13" s="13">
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="I13" s="13">
         <v>3.5</v>
       </c>
-      <c r="J13" s="8">
-        <v>2.1</v>
+      <c r="J13" s="12">
+        <v>5.25</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1248,10 +1248,10 @@
         <v>38</v>
       </c>
       <c r="D14" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-7</v>
@@ -1260,13 +1260,13 @@
         <v>-16.5</v>
       </c>
       <c r="H14" s="16">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="I14" s="16">
         <v>9.5</v>
       </c>
       <c r="J14" s="12">
-        <v>6.33</v>
+        <v>14.25</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1274,19 +1274,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>43</v>
       </c>
       <c r="F15" s="19">
         <v>-16.5</v>
@@ -1309,19 +1309,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>45</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>46</v>
       </c>
       <c r="F16" s="22">
         <v>-22</v>
@@ -1344,19 +1344,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>48</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>49</v>
       </c>
       <c r="F17" s="25">
         <v>-25.5</v>
@@ -1365,13 +1365,13 @@
         <v>-39.7</v>
       </c>
       <c r="H17" s="25">
-        <v>1.42</v>
+        <v>3.42</v>
       </c>
       <c r="I17" s="25">
         <v>14.2</v>
       </c>
-      <c r="J17" s="12">
-        <v>10.02</v>
+      <c r="J17" s="8">
+        <v>4.16</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1379,16 +1379,16 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>49</v>
       </c>
       <c r="E18" s="30" t="s">
         <v>52</v>
@@ -1400,13 +1400,13 @@
         <v>-44.24</v>
       </c>
       <c r="H18" s="28">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="I18" s="28">
         <v>4.54</v>
       </c>
       <c r="J18" s="8">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1625,13 +1625,13 @@
         <v>-7</v>
       </c>
       <c r="G4" s="13">
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="H4" s="13">
         <v>3.5</v>
       </c>
-      <c r="I4" s="8">
-        <v>2.1</v>
+      <c r="I4" s="12">
+        <v>5.25</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1654,13 +1654,13 @@
         <v>-16.5</v>
       </c>
       <c r="G5" s="16">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="H5" s="16">
         <v>9.5</v>
       </c>
       <c r="I5" s="12">
-        <v>6.33</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1700,7 +1700,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1729,7 +1729,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1741,13 +1741,13 @@
         <v>-39.7</v>
       </c>
       <c r="G8" s="25">
-        <v>1.42</v>
+        <v>3.42</v>
       </c>
       <c r="H8" s="25">
         <v>14.2</v>
       </c>
-      <c r="I8" s="12">
-        <v>10.02</v>
+      <c r="I8" s="8">
+        <v>4.16</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1770,13 +1770,13 @@
         <v>-44.24</v>
       </c>
       <c r="G9" s="28">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="H9" s="28">
         <v>4.54</v>
       </c>
       <c r="I9" s="8">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1799,13 +1799,13 @@
         <v>-44.24</v>
       </c>
       <c r="G10" s="33">
-        <v>8.35</v>
+        <v>8.47</v>
       </c>
       <c r="H10" s="33">
         <v>44.24</v>
       </c>
       <c r="I10" s="33">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
     </row>
   </sheetData>
